--- a/attendance.xlsx
+++ b/attendance.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\attendance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{450643CD-6FD5-48DE-94EA-BC600F1AE23D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56230D62-CEC7-4F70-AD05-90FAFD017B75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{773F372C-DF7E-4334-BF41-6DB0CC7AC205}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{773F372C-DF7E-4334-BF41-6DB0CC7AC205}"/>
   </bookViews>
   <sheets>
     <sheet name="BSIT1B" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="65">
   <si>
     <t>STUDENT NAME</t>
   </si>
@@ -231,6 +231,12 @@
   </si>
   <si>
     <t>25-00794</t>
+  </si>
+  <si>
+    <t>Yumul, Niccolo Franco Sta.</t>
+  </si>
+  <si>
+    <t>24-00610</t>
   </si>
 </sst>
 </file>
@@ -1026,7 +1032,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{192D3C0D-92A4-42D9-AF0F-CA33BE2906A4}">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.44140625" bestFit="1" customWidth="1"/>
@@ -1207,6 +1213,17 @@
         <v>39</v>
       </c>
       <c r="C16" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>63</v>
+      </c>
+      <c r="B17" t="s">
+        <v>64</v>
+      </c>
+      <c r="C17" t="s">
         <v>25</v>
       </c>
     </row>
